--- a/farmer_forms/003_herdshare_agreement_form--farmer_forms.xlsx
+++ b/farmer_forms/003_herdshare_agreement_form--farmer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>farm_name</t>
+          <t>farm_name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Farm Name</t>
+          <t>Farm Name 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Share Term</t>
+          <t>Farm Share Term</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Farm Start Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Farm End Date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>share_amount</t>
+          <t>share_amount_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share Amount</t>
+          <t>Share Amount 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
